--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A11_A16_세부요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A11_A16_세부요청표_20261028_담당자반영.xlsx
@@ -2655,7 +2655,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 권고일 2026-11-10</t>
+          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 권고일 2026-11-12</t>
+          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 권고일 2026-11-12</t>
+          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 권고일 2026-11-10</t>
+          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
     </row>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A11_A16_세부요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A11_A16_세부요청표_20261028_담당자반영.xlsx
@@ -768,7 +768,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 대체자: 이광재 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
     </row>
